--- a/AMS/009-Little-Sunflower/Little Sunflower FY 25-26 V1.xlsx
+++ b/AMS/009-Little-Sunflower/Little Sunflower FY 25-26 V1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BHARAT\2025-2026\BCB\AMS\009-Little-Sunflower\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642647C3-008A-48FD-BD39-362FF693B5F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18282993-6E9C-4C56-B955-E3E18B69950E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="862" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="862" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BS" sheetId="1" r:id="rId1"/>
@@ -1902,13 +1902,13 @@
     <t>Govt. Certified Panel Auditor</t>
   </si>
   <si>
-    <t>[Panel No.: Mumbai-4/B2/1011404]</t>
-  </si>
-  <si>
     <t>Chairman                       Secretary                       Treasurer</t>
   </si>
   <si>
     <t>2025-2026</t>
+  </si>
+  <si>
+    <t>[Panel No.: Mumbai-4/C1/1011404]</t>
   </si>
 </sst>
 </file>
@@ -2966,7 +2966,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="292">
+  <cellXfs count="281">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3326,75 +3326,9 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3425,12 +3359,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3452,18 +3380,6 @@
     <xf numFmtId="1" fontId="38" fillId="0" borderId="20" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="0" borderId="27" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="0" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3476,62 +3392,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="30" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3540,9 +3405,7 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -3587,83 +3450,191 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="38" fillId="0" borderId="27" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="38" fillId="0" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -4039,52 +4010,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="193" t="s">
+      <c r="A1" s="245" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="193"/>
-      <c r="G1" s="193"/>
-      <c r="H1" s="193"/>
+      <c r="B1" s="245"/>
+      <c r="C1" s="245"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="245"/>
+      <c r="F1" s="245"/>
+      <c r="G1" s="245"/>
+      <c r="H1" s="245"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="175" t="s">
+      <c r="A2" s="246" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="175"/>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175"/>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
-      <c r="H2" s="175"/>
+      <c r="B2" s="246"/>
+      <c r="C2" s="246"/>
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="246"/>
+      <c r="H2" s="246"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="175" t="s">
+      <c r="A3" s="246" t="s">
         <v>231</v>
       </c>
-      <c r="B3" s="175"/>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
+      <c r="B3" s="246"/>
+      <c r="C3" s="246"/>
+      <c r="D3" s="246"/>
+      <c r="E3" s="246"/>
+      <c r="F3" s="246"/>
+      <c r="G3" s="246"/>
+      <c r="H3" s="246"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="173" t="s">
+      <c r="A4" s="244" t="s">
         <v>368</v>
       </c>
-      <c r="B4" s="173"/>
-      <c r="C4" s="173"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="173"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="173"/>
+      <c r="B4" s="244"/>
+      <c r="C4" s="244"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
     </row>
     <row r="5" spans="1:12" s="51" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="90"/>
@@ -4102,21 +4073,21 @@
       <c r="A6" s="76" t="s">
         <v>366</v>
       </c>
-      <c r="B6" s="176" t="s">
+      <c r="B6" s="247" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="176"/>
-      <c r="D6" s="244" t="s">
+      <c r="C6" s="247"/>
+      <c r="D6" s="199" t="s">
         <v>367</v>
       </c>
       <c r="E6" s="172" t="str">
         <f>A6</f>
         <v>Previous Year 2024-25</v>
       </c>
-      <c r="F6" s="177" t="s">
+      <c r="F6" s="248" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="178"/>
+      <c r="G6" s="249"/>
       <c r="H6" s="76" t="str">
         <f>D6</f>
         <v>Current Year 2025-26</v>
@@ -4124,12 +4095,12 @@
     </row>
     <row r="7" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A7" s="54"/>
-      <c r="B7" s="245" t="s">
+      <c r="B7" s="79" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="55"/>
-      <c r="D7" s="246"/>
-      <c r="E7" s="242"/>
+      <c r="D7" s="200"/>
+      <c r="E7" s="197"/>
       <c r="F7" s="79" t="s">
         <v>0</v>
       </c>
@@ -4140,14 +4111,14 @@
       <c r="A8" s="53">
         <v>100000</v>
       </c>
-      <c r="B8" s="247" t="s">
+      <c r="B8" t="s">
         <v>222</v>
       </c>
       <c r="C8" s="55"/>
-      <c r="D8" s="248">
+      <c r="D8" s="201">
         <v>100000</v>
       </c>
-      <c r="E8" s="242">
+      <c r="E8" s="197">
         <v>764</v>
       </c>
       <c r="F8" t="s">
@@ -4160,10 +4131,9 @@
     </row>
     <row r="9" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A9" s="16"/>
-      <c r="B9" s="247"/>
       <c r="C9" s="55"/>
-      <c r="D9" s="249"/>
-      <c r="E9" s="242">
+      <c r="D9" s="202"/>
+      <c r="E9" s="197">
         <v>14409</v>
       </c>
       <c r="F9" t="s">
@@ -4178,12 +4148,12 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="16"/>
-      <c r="B10" s="245" t="s">
+      <c r="B10" s="79" t="s">
         <v>221</v>
       </c>
       <c r="C10" s="55"/>
-      <c r="D10" s="249"/>
-      <c r="E10" s="242">
+      <c r="D10" s="202"/>
+      <c r="E10" s="197">
         <v>5895</v>
       </c>
       <c r="F10" t="s">
@@ -4205,14 +4175,14 @@
       <c r="A11" s="16">
         <v>14000</v>
       </c>
-      <c r="B11" s="247" t="s">
+      <c r="B11" t="s">
         <v>223</v>
       </c>
       <c r="C11" s="55"/>
-      <c r="D11" s="250">
+      <c r="D11" s="203">
         <v>14000</v>
       </c>
-      <c r="E11" s="242">
+      <c r="E11" s="197">
         <v>15608</v>
       </c>
       <c r="F11" t="s">
@@ -4228,10 +4198,9 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="16"/>
-      <c r="B12" s="247"/>
       <c r="C12" s="55"/>
-      <c r="D12" s="249"/>
-      <c r="E12" s="242">
+      <c r="D12" s="202"/>
+      <c r="E12" s="197">
         <v>236540.74</v>
       </c>
       <c r="F12" t="s">
@@ -4249,12 +4218,12 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="16"/>
-      <c r="B13" s="245" t="s">
+      <c r="B13" s="79" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="55"/>
-      <c r="D13" s="249"/>
-      <c r="E13" s="242"/>
+      <c r="D13" s="202"/>
+      <c r="E13" s="197"/>
       <c r="G13" s="55"/>
       <c r="H13" s="16"/>
       <c r="J13" s="46"/>
@@ -4263,15 +4232,15 @@
       <c r="A14" s="16">
         <v>627286</v>
       </c>
-      <c r="B14" s="247" t="s">
+      <c r="B14" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="55">
         <f>SUM(A14:A17)</f>
         <v>734254</v>
       </c>
-      <c r="D14" s="249"/>
-      <c r="E14" s="242"/>
+      <c r="D14" s="202"/>
+      <c r="E14" s="197"/>
       <c r="F14" s="79" t="s">
         <v>226</v>
       </c>
@@ -4283,15 +4252,15 @@
       <c r="A15" s="16">
         <v>23174</v>
       </c>
-      <c r="B15" s="247" t="s">
+      <c r="B15" t="s">
         <v>83</v>
       </c>
       <c r="C15" s="55">
         <f>IE!D46</f>
         <v>10602</v>
       </c>
-      <c r="D15" s="249"/>
-      <c r="E15" s="242">
+      <c r="D15" s="202"/>
+      <c r="E15" s="197">
         <v>500</v>
       </c>
       <c r="F15" t="s">
@@ -4307,14 +4276,14 @@
       <c r="A16" s="16">
         <v>300</v>
       </c>
-      <c r="B16" s="247" t="s">
+      <c r="B16" t="s">
         <v>38</v>
       </c>
       <c r="C16" s="55">
         <v>0</v>
       </c>
-      <c r="D16" s="249"/>
-      <c r="E16" s="242">
+      <c r="D16" s="202"/>
+      <c r="E16" s="197">
         <v>100</v>
       </c>
       <c r="F16" t="s">
@@ -4330,18 +4299,18 @@
       <c r="A17" s="16">
         <v>83494</v>
       </c>
-      <c r="B17" s="247" t="s">
+      <c r="B17" t="s">
         <v>115</v>
       </c>
       <c r="C17" s="96">
         <f>'FD Interest Working'!E117</f>
         <v>101228</v>
       </c>
-      <c r="D17" s="250">
+      <c r="D17" s="203">
         <f>SUM(C14:C17)</f>
         <v>846084</v>
       </c>
-      <c r="E17" s="242">
+      <c r="E17" s="197">
         <v>2500</v>
       </c>
       <c r="F17" t="s">
@@ -4355,12 +4324,12 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="16"/>
-      <c r="B18" s="245" t="s">
+      <c r="B18" s="79" t="s">
         <v>175</v>
       </c>
       <c r="C18" s="55"/>
-      <c r="D18" s="249"/>
-      <c r="E18" s="242">
+      <c r="D18" s="202"/>
+      <c r="E18" s="197">
         <v>8108609</v>
       </c>
       <c r="F18" s="79" t="s">
@@ -4378,15 +4347,15 @@
       <c r="A19" s="16">
         <v>74603</v>
       </c>
-      <c r="B19" s="247" t="s">
+      <c r="B19" t="s">
         <v>176</v>
       </c>
       <c r="C19" s="55">
         <f>SUM(A19:A22)</f>
         <v>96383</v>
       </c>
-      <c r="D19" s="249"/>
-      <c r="E19" s="242">
+      <c r="D19" s="202"/>
+      <c r="E19" s="197">
         <v>576281</v>
       </c>
       <c r="F19" t="s">
@@ -4406,14 +4375,14 @@
       <c r="A20" s="16">
         <v>0</v>
       </c>
-      <c r="B20" s="247" t="s">
+      <c r="B20" t="s">
         <v>168</v>
       </c>
       <c r="C20" s="55">
         <v>0</v>
       </c>
-      <c r="D20" s="250"/>
-      <c r="E20" s="242"/>
+      <c r="D20" s="203"/>
+      <c r="E20" s="197"/>
       <c r="G20" s="55"/>
       <c r="H20" s="16"/>
       <c r="J20" s="46"/>
@@ -4422,14 +4391,14 @@
       <c r="A21" s="16">
         <v>10000</v>
       </c>
-      <c r="B21" s="247" t="s">
+      <c r="B21" t="s">
         <v>324</v>
       </c>
       <c r="C21" s="55">
         <v>0</v>
       </c>
-      <c r="D21" s="250"/>
-      <c r="E21" s="242"/>
+      <c r="D21" s="203"/>
+      <c r="E21" s="197"/>
       <c r="F21" s="79" t="s">
         <v>3</v>
       </c>
@@ -4441,18 +4410,18 @@
       <c r="A22" s="16">
         <v>11780</v>
       </c>
-      <c r="B22" s="247" t="s">
+      <c r="B22" t="s">
         <v>115</v>
       </c>
       <c r="C22" s="92">
         <f>'FD Interest Working'!E115</f>
         <v>7902</v>
       </c>
-      <c r="D22" s="250">
+      <c r="D22" s="203">
         <f>SUM(C19:C22)</f>
         <v>104285</v>
       </c>
-      <c r="E22" s="242">
+      <c r="E22" s="197">
         <v>12131.5</v>
       </c>
       <c r="F22" t="s">
@@ -4466,12 +4435,12 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="16"/>
-      <c r="B23" s="245" t="s">
+      <c r="B23" s="79" t="s">
         <v>39</v>
       </c>
       <c r="C23" s="55"/>
-      <c r="D23" s="249"/>
-      <c r="E23" s="242"/>
+      <c r="D23" s="202"/>
+      <c r="E23" s="197"/>
       <c r="G23" s="55"/>
       <c r="H23" s="16"/>
       <c r="J23" s="46"/>
@@ -4481,15 +4450,15 @@
       <c r="A24" s="16">
         <v>1389293</v>
       </c>
-      <c r="B24" s="247" t="s">
+      <c r="B24" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="55">
         <f>SUM(A24:A26)</f>
         <v>1584118</v>
       </c>
-      <c r="D24" s="249"/>
-      <c r="E24" s="242"/>
+      <c r="D24" s="202"/>
+      <c r="E24" s="197"/>
       <c r="F24" s="79" t="s">
         <v>4</v>
       </c>
@@ -4501,14 +4470,14 @@
       <c r="A25" s="16">
         <v>103200</v>
       </c>
-      <c r="B25" s="247" t="s">
+      <c r="B25" t="s">
         <v>38</v>
       </c>
       <c r="C25" s="55">
         <v>54000</v>
       </c>
-      <c r="D25" s="249"/>
-      <c r="E25" s="242">
+      <c r="D25" s="202"/>
+      <c r="E25" s="197">
         <v>35838000</v>
       </c>
       <c r="F25" t="s">
@@ -4524,18 +4493,18 @@
       <c r="A26" s="16">
         <v>91625</v>
       </c>
-      <c r="B26" s="247" t="s">
+      <c r="B26" t="s">
         <v>115</v>
       </c>
       <c r="C26" s="92">
         <f>'FD Interest Working'!E114</f>
         <v>108594</v>
       </c>
-      <c r="D26" s="250">
+      <c r="D26" s="203">
         <f>SUM(C24:C26)</f>
         <v>1746712</v>
       </c>
-      <c r="E26" s="242">
+      <c r="E26" s="197">
         <v>189800</v>
       </c>
       <c r="F26" s="79" t="s">
@@ -4550,12 +4519,12 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="54"/>
-      <c r="B27" s="245" t="s">
+      <c r="B27" s="79" t="s">
         <v>13</v>
       </c>
       <c r="C27" s="55"/>
-      <c r="D27" s="249"/>
-      <c r="E27" s="242"/>
+      <c r="D27" s="202"/>
+      <c r="E27" s="197"/>
       <c r="F27" s="2"/>
       <c r="G27" s="55"/>
       <c r="H27" s="16"/>
@@ -4565,15 +4534,15 @@
       <c r="A28" s="16">
         <v>1069196</v>
       </c>
-      <c r="B28" s="247" t="s">
+      <c r="B28" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="55">
         <f>SUM(A28:A30)</f>
         <v>1203632</v>
       </c>
-      <c r="D28" s="249"/>
-      <c r="E28" s="242"/>
+      <c r="D28" s="202"/>
+      <c r="E28" s="197"/>
       <c r="F28" s="79" t="s">
         <v>5</v>
       </c>
@@ -4585,14 +4554,14 @@
       <c r="A29" s="16">
         <v>58224</v>
       </c>
-      <c r="B29" s="247" t="s">
+      <c r="B29" t="s">
         <v>14</v>
       </c>
       <c r="C29" s="55">
         <v>58224</v>
       </c>
-      <c r="D29" s="249"/>
-      <c r="E29" s="242">
+      <c r="D29" s="202"/>
+      <c r="E29" s="197">
         <v>2870</v>
       </c>
       <c r="F29" t="s">
@@ -4609,30 +4578,30 @@
       <c r="A30" s="16">
         <v>76212</v>
       </c>
-      <c r="B30" s="247" t="s">
+      <c r="B30" t="s">
         <v>115</v>
       </c>
       <c r="C30" s="92">
         <f>'FD Interest Working'!E122</f>
         <v>86946</v>
       </c>
-      <c r="D30" s="250">
+      <c r="D30" s="203">
         <f>SUM(C28:C30)</f>
         <v>1348802</v>
       </c>
-      <c r="E30" s="242"/>
+      <c r="E30" s="197"/>
       <c r="G30" s="55"/>
       <c r="H30" s="16"/>
       <c r="J30" s="46"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="16"/>
-      <c r="B31" s="245" t="s">
+      <c r="B31" s="79" t="s">
         <v>40</v>
       </c>
       <c r="C31" s="55"/>
-      <c r="D31" s="249"/>
-      <c r="E31" s="242"/>
+      <c r="D31" s="202"/>
+      <c r="E31" s="197"/>
       <c r="F31" s="79" t="s">
         <v>228</v>
       </c>
@@ -4644,15 +4613,15 @@
       <c r="A32" s="16">
         <v>4563998</v>
       </c>
-      <c r="B32" s="247" t="s">
+      <c r="B32" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="55">
         <f>SUM(A32:A35)</f>
         <v>3453942</v>
       </c>
-      <c r="D32" s="249"/>
-      <c r="E32" s="242">
+      <c r="D32" s="202"/>
+      <c r="E32" s="197">
         <v>12286</v>
       </c>
       <c r="F32" t="s">
@@ -4668,14 +4637,14 @@
       <c r="A33" s="16">
         <v>175056</v>
       </c>
-      <c r="B33" s="247" t="s">
+      <c r="B33" t="s">
         <v>14</v>
       </c>
       <c r="C33" s="55">
         <v>175056</v>
       </c>
-      <c r="D33" s="249"/>
-      <c r="E33" s="242">
+      <c r="D33" s="202"/>
+      <c r="E33" s="197">
         <v>4295</v>
       </c>
       <c r="F33" t="s">
@@ -4694,15 +4663,15 @@
       <c r="A34" s="16">
         <v>-1489986</v>
       </c>
-      <c r="B34" s="247" t="s">
+      <c r="B34" t="s">
         <v>301</v>
       </c>
       <c r="C34" s="55">
         <f>IE!C20</f>
         <v>-152099</v>
       </c>
-      <c r="D34" s="249"/>
-      <c r="E34" s="242"/>
+      <c r="D34" s="202"/>
+      <c r="E34" s="197"/>
       <c r="G34" s="55"/>
       <c r="H34" s="28"/>
       <c r="J34" s="46"/>
@@ -4711,30 +4680,30 @@
       <c r="A35" s="16">
         <v>204874</v>
       </c>
-      <c r="B35" s="247" t="s">
+      <c r="B35" t="s">
         <v>115</v>
       </c>
       <c r="C35" s="92">
         <f>'FD Interest Working'!E119</f>
         <v>237133</v>
       </c>
-      <c r="D35" s="250">
+      <c r="D35" s="203">
         <f>SUM(C32:C35)</f>
         <v>3714032</v>
       </c>
-      <c r="E35" s="242"/>
+      <c r="E35" s="197"/>
       <c r="G35" s="55"/>
       <c r="H35" s="16"/>
       <c r="J35" s="46"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="16"/>
-      <c r="B36" s="245" t="s">
+      <c r="B36" s="79" t="s">
         <v>116</v>
       </c>
       <c r="C36" s="55"/>
-      <c r="D36" s="249"/>
-      <c r="E36" s="242"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="197"/>
       <c r="F36" s="79" t="s">
         <v>229</v>
       </c>
@@ -4746,15 +4715,15 @@
       <c r="A37" s="16">
         <v>719610</v>
       </c>
-      <c r="B37" s="247" t="s">
+      <c r="B37" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="55">
         <f>SUM(A37:A38)</f>
         <v>767792</v>
       </c>
-      <c r="D37" s="249"/>
-      <c r="E37" s="242">
+      <c r="D37" s="202"/>
+      <c r="E37" s="197">
         <v>50131</v>
       </c>
       <c r="F37" t="s">
@@ -4773,18 +4742,18 @@
       <c r="A38" s="16">
         <v>48182</v>
       </c>
-      <c r="B38" s="247" t="s">
+      <c r="B38" t="s">
         <v>115</v>
       </c>
       <c r="C38" s="92">
         <f>'FD Interest Working'!E116</f>
         <v>53843</v>
       </c>
-      <c r="D38" s="250">
+      <c r="D38" s="203">
         <f>SUM(C37:C38)</f>
         <v>821635</v>
       </c>
-      <c r="E38" s="242"/>
+      <c r="E38" s="197"/>
       <c r="G38" s="55"/>
       <c r="H38" s="16"/>
       <c r="J38" s="46"/>
@@ -4792,12 +4761,12 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="16"/>
-      <c r="B39" s="245" t="s">
+      <c r="B39" s="79" t="s">
         <v>69</v>
       </c>
       <c r="C39" s="55"/>
-      <c r="D39" s="249"/>
-      <c r="E39" s="242"/>
+      <c r="D39" s="202"/>
+      <c r="E39" s="197"/>
       <c r="G39" s="55"/>
       <c r="H39" s="16"/>
       <c r="J39" s="46"/>
@@ -4806,15 +4775,15 @@
       <c r="A40" s="16">
         <v>19894</v>
       </c>
-      <c r="B40" s="247" t="s">
+      <c r="B40" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="55">
         <f>SUM(A40:A42)</f>
         <v>1103</v>
       </c>
-      <c r="D40" s="249"/>
-      <c r="E40" s="242"/>
+      <c r="D40" s="202"/>
+      <c r="E40" s="197"/>
       <c r="G40" s="55"/>
       <c r="H40" s="16"/>
       <c r="J40" s="46"/>
@@ -4823,14 +4792,14 @@
       <c r="A41" s="16">
         <v>5376</v>
       </c>
-      <c r="B41" s="247" t="s">
+      <c r="B41" t="s">
         <v>14</v>
       </c>
       <c r="C41" s="55">
         <v>5376</v>
       </c>
-      <c r="D41" s="250"/>
-      <c r="E41" s="242"/>
+      <c r="D41" s="203"/>
+      <c r="E41" s="197"/>
       <c r="G41" s="55"/>
       <c r="H41" s="16"/>
       <c r="J41" s="46"/>
@@ -4839,39 +4808,38 @@
       <c r="A42" s="16">
         <v>-24167</v>
       </c>
-      <c r="B42" s="247" t="s">
+      <c r="B42" t="s">
         <v>278</v>
       </c>
       <c r="C42" s="96">
         <v>0</v>
       </c>
-      <c r="D42" s="250">
+      <c r="D42" s="203">
         <f>SUM(C40:C42)</f>
         <v>6479</v>
       </c>
-      <c r="E42" s="242"/>
+      <c r="E42" s="197"/>
       <c r="G42" s="55"/>
       <c r="H42" s="16"/>
       <c r="J42" s="46"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="16"/>
-      <c r="B43" s="247"/>
       <c r="C43" s="55"/>
-      <c r="D43" s="249"/>
-      <c r="E43" s="242"/>
+      <c r="D43" s="202"/>
+      <c r="E43" s="197"/>
       <c r="G43" s="55"/>
       <c r="H43" s="16"/>
       <c r="J43" s="46"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="16"/>
-      <c r="B44" s="245" t="s">
+      <c r="B44" s="79" t="s">
         <v>234</v>
       </c>
       <c r="C44" s="55"/>
-      <c r="D44" s="249"/>
-      <c r="E44" s="242"/>
+      <c r="D44" s="202"/>
+      <c r="E44" s="197"/>
       <c r="G44" s="55"/>
       <c r="H44" s="16"/>
       <c r="J44" s="46"/>
@@ -4880,15 +4848,15 @@
       <c r="A45" s="16">
         <v>84000</v>
       </c>
-      <c r="B45" s="247" t="s">
+      <c r="B45" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="55">
         <f>'Sch III, IV, V, VI &amp; VII'!D20</f>
         <v>80000</v>
       </c>
-      <c r="D45" s="249"/>
-      <c r="E45" s="242"/>
+      <c r="D45" s="202"/>
+      <c r="E45" s="197"/>
       <c r="G45" s="55"/>
       <c r="H45" s="16"/>
       <c r="J45" s="46"/>
@@ -4897,14 +4865,14 @@
       <c r="A46" s="16">
         <v>0</v>
       </c>
-      <c r="B46" s="247" t="s">
+      <c r="B46" t="s">
         <v>38</v>
       </c>
       <c r="C46" s="55">
         <v>0</v>
       </c>
-      <c r="D46" s="249"/>
-      <c r="E46" s="242"/>
+      <c r="D46" s="202"/>
+      <c r="E46" s="197"/>
       <c r="G46" s="55"/>
       <c r="H46" s="16"/>
       <c r="J46" s="46"/>
@@ -4913,14 +4881,14 @@
       <c r="A47" s="16">
         <v>0</v>
       </c>
-      <c r="B47" s="247" t="s">
+      <c r="B47" t="s">
         <v>177</v>
       </c>
       <c r="C47" s="55">
         <v>0</v>
       </c>
-      <c r="D47" s="250"/>
-      <c r="E47" s="242"/>
+      <c r="D47" s="203"/>
+      <c r="E47" s="197"/>
       <c r="G47" s="55"/>
       <c r="H47" s="16"/>
       <c r="J47" s="46"/>
@@ -4929,27 +4897,26 @@
       <c r="A48" s="16">
         <v>-4000</v>
       </c>
-      <c r="B48" s="247" t="s">
+      <c r="B48" t="s">
         <v>145</v>
       </c>
       <c r="C48" s="92">
         <v>0</v>
       </c>
-      <c r="D48" s="250">
+      <c r="D48" s="203">
         <f>SUM(C45:C48)</f>
         <v>80000</v>
       </c>
-      <c r="E48" s="242"/>
+      <c r="E48" s="197"/>
       <c r="G48" s="55"/>
       <c r="H48" s="16"/>
       <c r="J48" s="46"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="16"/>
-      <c r="B49" s="247"/>
       <c r="C49" s="55"/>
-      <c r="D49" s="249"/>
-      <c r="E49" s="242"/>
+      <c r="D49" s="202"/>
+      <c r="E49" s="197"/>
       <c r="G49" s="55"/>
       <c r="H49" s="16"/>
       <c r="J49" s="46"/>
@@ -4958,24 +4925,23 @@
       <c r="A50" s="16">
         <v>35838000</v>
       </c>
-      <c r="B50" s="247" t="s">
+      <c r="B50" t="s">
         <v>85</v>
       </c>
       <c r="C50" s="55"/>
-      <c r="D50" s="250">
+      <c r="D50" s="203">
         <v>35838000</v>
       </c>
-      <c r="E50" s="242"/>
+      <c r="E50" s="197"/>
       <c r="G50" s="55"/>
       <c r="H50" s="16"/>
       <c r="J50" s="46"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="54"/>
-      <c r="B51" s="247"/>
       <c r="C51" s="55"/>
-      <c r="D51" s="249"/>
-      <c r="E51" s="242"/>
+      <c r="D51" s="202"/>
+      <c r="E51" s="197"/>
       <c r="G51" s="55"/>
       <c r="H51" s="16"/>
       <c r="J51" s="46"/>
@@ -4984,37 +4950,36 @@
       <c r="A52" s="16">
         <v>23558</v>
       </c>
-      <c r="B52" s="245" t="s">
+      <c r="B52" s="79" t="s">
         <v>235</v>
       </c>
       <c r="C52" s="55"/>
-      <c r="D52" s="250">
+      <c r="D52" s="203">
         <f>'Sch III, IV, V, VI &amp; VII'!D29</f>
         <v>31977</v>
       </c>
-      <c r="E52" s="242"/>
+      <c r="E52" s="197"/>
       <c r="G52" s="55"/>
       <c r="H52" s="16"/>
       <c r="J52" s="46"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="16"/>
-      <c r="B53" s="247"/>
       <c r="C53" s="55"/>
-      <c r="D53" s="249"/>
-      <c r="E53" s="242"/>
+      <c r="D53" s="202"/>
+      <c r="E53" s="197"/>
       <c r="G53" s="55"/>
       <c r="H53" s="16"/>
       <c r="J53" s="46"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="16"/>
-      <c r="B54" s="245" t="s">
+      <c r="B54" s="79" t="s">
         <v>15</v>
       </c>
       <c r="C54" s="55"/>
-      <c r="D54" s="249"/>
-      <c r="E54" s="242"/>
+      <c r="D54" s="202"/>
+      <c r="E54" s="197"/>
       <c r="G54" s="55"/>
       <c r="H54" s="16"/>
       <c r="J54" s="46"/>
@@ -5023,25 +4988,24 @@
       <c r="A55" s="16">
         <v>61831</v>
       </c>
-      <c r="B55" s="245" t="s">
+      <c r="B55" s="79" t="s">
         <v>236</v>
       </c>
       <c r="C55" s="55"/>
-      <c r="D55" s="250">
+      <c r="D55" s="203">
         <f>'Sch III, IV, V, VI &amp; VII'!D46</f>
         <v>45591.520000000004</v>
       </c>
-      <c r="E55" s="242"/>
+      <c r="E55" s="197"/>
       <c r="G55" s="55"/>
       <c r="H55" s="16"/>
       <c r="J55" s="46"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="16"/>
-      <c r="B56" s="247"/>
       <c r="C56" s="55"/>
-      <c r="D56" s="249"/>
-      <c r="E56" s="242"/>
+      <c r="D56" s="202"/>
+      <c r="E56" s="197"/>
       <c r="G56" s="55"/>
       <c r="H56" s="16"/>
       <c r="I56" s="56"/>
@@ -5049,12 +5013,12 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="16"/>
-      <c r="B57" s="245" t="s">
+      <c r="B57" s="79" t="s">
         <v>18</v>
       </c>
       <c r="C57" s="55"/>
-      <c r="D57" s="249"/>
-      <c r="E57" s="242"/>
+      <c r="D57" s="202"/>
+      <c r="E57" s="197"/>
       <c r="G57" s="55"/>
       <c r="H57" s="16"/>
       <c r="J57" s="46"/>
@@ -5064,15 +5028,15 @@
       <c r="A58" s="16">
         <v>1138986.99</v>
       </c>
-      <c r="B58" s="247" t="s">
+      <c r="B58" t="s">
         <v>8</v>
       </c>
       <c r="C58" s="55">
         <f>SUM(A58:A61)</f>
         <v>1212107.24</v>
       </c>
-      <c r="D58" s="249"/>
-      <c r="E58" s="242"/>
+      <c r="D58" s="202"/>
+      <c r="E58" s="197"/>
       <c r="F58" s="47"/>
       <c r="G58" s="55"/>
       <c r="H58" s="16"/>
@@ -5082,14 +5046,14 @@
       <c r="A59" s="16">
         <v>3600</v>
       </c>
-      <c r="B59" s="245" t="s">
+      <c r="B59" s="79" t="s">
         <v>325</v>
       </c>
       <c r="C59" s="55">
         <v>0</v>
       </c>
-      <c r="D59" s="249"/>
-      <c r="E59" s="242"/>
+      <c r="D59" s="202"/>
+      <c r="E59" s="197"/>
       <c r="G59" s="55"/>
       <c r="H59" s="16"/>
       <c r="I59" s="47"/>
@@ -5099,14 +5063,14 @@
       <c r="A60" s="16">
         <v>0</v>
       </c>
-      <c r="B60" s="245" t="s">
+      <c r="B60" s="79" t="s">
         <v>599</v>
       </c>
       <c r="C60" s="55">
         <v>2366</v>
       </c>
-      <c r="D60" s="249"/>
-      <c r="E60" s="242"/>
+      <c r="D60" s="202"/>
+      <c r="E60" s="197"/>
       <c r="G60" s="55"/>
       <c r="H60" s="16"/>
       <c r="J60" s="46"/>
@@ -5115,18 +5079,18 @@
       <c r="A61" s="50">
         <v>69520.25</v>
       </c>
-      <c r="B61" s="247" t="s">
+      <c r="B61" t="s">
         <v>302</v>
       </c>
       <c r="C61" s="92">
         <f>IE!D47</f>
         <v>31804.589999999967</v>
       </c>
-      <c r="D61" s="250">
+      <c r="D61" s="203">
         <f>SUM(C58:C61)</f>
         <v>1246277.83</v>
       </c>
-      <c r="E61" s="242"/>
+      <c r="E61" s="197"/>
       <c r="G61" s="55"/>
       <c r="H61" s="16"/>
       <c r="J61" s="46"/>
@@ -5136,22 +5100,22 @@
         <f>SUM(A10:A61)</f>
         <v>45070720.240000002</v>
       </c>
-      <c r="B62" s="180" t="s">
+      <c r="B62" s="252" t="s">
         <v>28</v>
       </c>
-      <c r="C62" s="181"/>
-      <c r="D62" s="251">
+      <c r="C62" s="253"/>
+      <c r="D62" s="204">
         <f>SUM(D9:D61)</f>
         <v>45843875.350000001</v>
       </c>
-      <c r="E62" s="243">
+      <c r="E62" s="198">
         <f>SUM(E8:E61)</f>
         <v>45070720.240000002</v>
       </c>
-      <c r="F62" s="179" t="s">
+      <c r="F62" s="250" t="s">
         <v>28</v>
       </c>
-      <c r="G62" s="291"/>
+      <c r="G62" s="251"/>
       <c r="H62" s="94">
         <f>SUM(H8:H61)</f>
         <v>45844301.350000001</v>
@@ -5159,75 +5123,75 @@
       <c r="J62" s="46"/>
     </row>
     <row r="63" spans="1:11" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="194"/>
+      <c r="A63" s="173"/>
       <c r="B63" s="152"/>
       <c r="C63" s="19"/>
       <c r="D63" s="70"/>
-      <c r="E63" s="195"/>
-      <c r="F63" s="195"/>
-      <c r="G63" s="195"/>
-      <c r="H63" s="196"/>
+      <c r="E63" s="254"/>
+      <c r="F63" s="254"/>
+      <c r="G63" s="254"/>
+      <c r="H63" s="174"/>
       <c r="J63" s="46"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A64" s="199" t="s">
+      <c r="A64" s="177" t="s">
         <v>84</v>
       </c>
-      <c r="B64" s="197"/>
-      <c r="C64" s="197"/>
-      <c r="D64" s="200"/>
-      <c r="E64" s="201"/>
-      <c r="F64" s="197"/>
-      <c r="G64" s="201"/>
-      <c r="H64" s="202"/>
+      <c r="B64" s="175"/>
+      <c r="C64" s="175"/>
+      <c r="D64" s="178"/>
+      <c r="E64" s="179"/>
+      <c r="F64" s="175"/>
+      <c r="G64" s="179"/>
+      <c r="H64" s="180"/>
       <c r="I64" s="56"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" s="203"/>
-      <c r="B65" s="197"/>
-      <c r="C65" s="197"/>
-      <c r="D65" s="204"/>
-      <c r="E65" s="205"/>
-      <c r="F65" s="206" t="s">
+      <c r="A65" s="181"/>
+      <c r="B65" s="175"/>
+      <c r="C65" s="175"/>
+      <c r="D65" s="182"/>
+      <c r="E65" s="183"/>
+      <c r="F65" s="255" t="s">
         <v>610</v>
       </c>
-      <c r="G65" s="206"/>
-      <c r="H65" s="207"/>
+      <c r="G65" s="255"/>
+      <c r="H65" s="256"/>
       <c r="I65" s="56"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" s="203"/>
-      <c r="B66" s="197"/>
-      <c r="C66" s="197"/>
-      <c r="D66" s="204"/>
-      <c r="E66" s="205"/>
-      <c r="F66" s="208"/>
-      <c r="G66" s="205"/>
-      <c r="H66" s="209"/>
+      <c r="A66" s="181"/>
+      <c r="B66" s="175"/>
+      <c r="C66" s="175"/>
+      <c r="D66" s="182"/>
+      <c r="E66" s="183"/>
+      <c r="F66" s="184"/>
+      <c r="G66" s="183"/>
+      <c r="H66" s="185"/>
       <c r="I66" s="56"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A67" s="203"/>
-      <c r="B67" s="197"/>
-      <c r="C67" s="197"/>
-      <c r="D67" s="204"/>
-      <c r="E67" s="205"/>
-      <c r="F67" s="208"/>
-      <c r="G67" s="205"/>
-      <c r="H67" s="209"/>
+      <c r="A67" s="181"/>
+      <c r="B67" s="175"/>
+      <c r="C67" s="175"/>
+      <c r="D67" s="182"/>
+      <c r="E67" s="183"/>
+      <c r="F67" s="184"/>
+      <c r="G67" s="183"/>
+      <c r="H67" s="185"/>
       <c r="I67" s="56"/>
     </row>
     <row r="68" spans="1:12" s="95" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="211" t="s">
+      <c r="A68" s="187" t="s">
         <v>611</v>
       </c>
-      <c r="B68" s="212"/>
-      <c r="C68" s="213"/>
-      <c r="D68" s="204"/>
-      <c r="E68" s="205"/>
-      <c r="F68" s="208"/>
-      <c r="G68" s="205"/>
-      <c r="H68" s="209"/>
+      <c r="B68" s="188"/>
+      <c r="C68" s="189"/>
+      <c r="D68" s="182"/>
+      <c r="E68" s="183"/>
+      <c r="F68" s="184"/>
+      <c r="G68" s="183"/>
+      <c r="H68" s="185"/>
       <c r="I68" s="151">
         <f>A62-E62</f>
         <v>0</v>
@@ -5239,48 +5203,48 @@
       <c r="K68" s="129"/>
       <c r="L68" s="129"/>
     </row>
-    <row r="69" spans="1:12" s="197" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="214" t="s">
+    <row r="69" spans="1:12" s="175" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="190" t="s">
         <v>612</v>
       </c>
-      <c r="B69" s="212"/>
-      <c r="C69" s="213"/>
-      <c r="D69" s="204"/>
-      <c r="E69" s="205"/>
-      <c r="F69" s="208"/>
-      <c r="G69" s="205"/>
-      <c r="H69" s="209"/>
-      <c r="J69" s="198"/>
-    </row>
-    <row r="70" spans="1:12" s="197" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="214" t="s">
+      <c r="B69" s="188"/>
+      <c r="C69" s="189"/>
+      <c r="D69" s="182"/>
+      <c r="E69" s="183"/>
+      <c r="F69" s="184"/>
+      <c r="G69" s="183"/>
+      <c r="H69" s="185"/>
+      <c r="J69" s="176"/>
+    </row>
+    <row r="70" spans="1:12" s="175" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="190" t="s">
+        <v>615</v>
+      </c>
+      <c r="B70" s="188"/>
+      <c r="C70" s="189"/>
+      <c r="D70" s="182"/>
+      <c r="E70" s="183"/>
+      <c r="F70" s="257" t="s">
         <v>613</v>
       </c>
-      <c r="B70" s="212"/>
-      <c r="C70" s="213"/>
-      <c r="D70" s="204"/>
-      <c r="E70" s="205"/>
-      <c r="F70" s="215" t="s">
-        <v>614</v>
-      </c>
-      <c r="G70" s="215"/>
-      <c r="H70" s="216"/>
-      <c r="J70" s="198"/>
-    </row>
-    <row r="71" spans="1:12" s="197" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="217">
+      <c r="G70" s="257"/>
+      <c r="H70" s="258"/>
+      <c r="J70" s="176"/>
+    </row>
+    <row r="71" spans="1:12" s="175" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="242">
         <v>46235</v>
       </c>
-      <c r="B71" s="218"/>
-      <c r="C71" s="218"/>
-      <c r="D71" s="219"/>
-      <c r="E71" s="220"/>
-      <c r="F71" s="221"/>
-      <c r="G71" s="220"/>
-      <c r="H71" s="222"/>
-      <c r="J71" s="198"/>
-    </row>
-    <row r="72" spans="1:12" s="197" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="243"/>
+      <c r="C71" s="243"/>
+      <c r="D71" s="191"/>
+      <c r="E71" s="192"/>
+      <c r="F71" s="193"/>
+      <c r="G71" s="192"/>
+      <c r="H71" s="194"/>
+      <c r="J71" s="176"/>
+    </row>
+    <row r="72" spans="1:12" s="175" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="52"/>
       <c r="B72"/>
       <c r="C72" s="56"/>
@@ -5289,9 +5253,9 @@
       <c r="F72"/>
       <c r="G72" s="56"/>
       <c r="H72" s="52"/>
-      <c r="J72" s="198"/>
-    </row>
-    <row r="73" spans="1:12" s="197" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J72" s="176"/>
+    </row>
+    <row r="73" spans="1:12" s="175" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="52"/>
       <c r="B73"/>
       <c r="C73" s="56"/>
@@ -5300,9 +5264,9 @@
       <c r="F73"/>
       <c r="G73" s="56"/>
       <c r="H73" s="52"/>
-      <c r="I73" s="210"/>
-    </row>
-    <row r="74" spans="1:12" s="197" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="I73" s="186"/>
+    </row>
+    <row r="74" spans="1:12" s="175" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="52"/>
       <c r="B74"/>
       <c r="C74" s="56"/>
@@ -5311,9 +5275,9 @@
       <c r="F74"/>
       <c r="G74" s="56"/>
       <c r="H74" s="52"/>
-      <c r="I74" s="210"/>
-    </row>
-    <row r="75" spans="1:12" s="197" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="I74" s="186"/>
+    </row>
+    <row r="75" spans="1:12" s="175" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="52"/>
       <c r="B75"/>
       <c r="C75" s="56"/>
@@ -5322,7 +5286,7 @@
       <c r="F75"/>
       <c r="G75" s="56"/>
       <c r="H75" s="52"/>
-      <c r="I75" s="210"/>
+      <c r="I75" s="186"/>
     </row>
     <row r="76" spans="1:12" s="95" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="52"/>
@@ -5342,7 +5306,7 @@
         <v>-426</v>
       </c>
     </row>
-    <row r="77" spans="1:12" s="197" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" s="175" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="52"/>
       <c r="B77"/>
       <c r="C77" s="56"/>
@@ -5397,63 +5361,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="224" t="s">
+      <c r="A1" s="259" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="225"/>
-      <c r="C1" s="225"/>
-      <c r="D1" s="225"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
-      <c r="G1" s="225"/>
-      <c r="H1" s="226"/>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="261"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="227" t="str">
+      <c r="A2" s="266" t="str">
         <f>BS!A2</f>
         <v>(Regd. No. BOM/HSG/3365/1972)</v>
       </c>
-      <c r="B2" s="228"/>
-      <c r="C2" s="228"/>
-      <c r="D2" s="228"/>
-      <c r="E2" s="228"/>
-      <c r="F2" s="228"/>
-      <c r="G2" s="228"/>
-      <c r="H2" s="229"/>
+      <c r="B2" s="246"/>
+      <c r="C2" s="246"/>
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="246"/>
+      <c r="H2" s="267"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="227" t="s">
+      <c r="A3" s="266" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="228"/>
-      <c r="C3" s="228"/>
-      <c r="D3" s="228"/>
-      <c r="E3" s="228"/>
-      <c r="F3" s="228"/>
-      <c r="G3" s="228"/>
-      <c r="H3" s="229"/>
+      <c r="B3" s="246"/>
+      <c r="C3" s="246"/>
+      <c r="D3" s="246"/>
+      <c r="E3" s="246"/>
+      <c r="F3" s="246"/>
+      <c r="G3" s="246"/>
+      <c r="H3" s="267"/>
     </row>
     <row r="4" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A4" s="230" t="s">
+      <c r="A4" s="262" t="s">
         <v>369</v>
       </c>
-      <c r="B4" s="223"/>
-      <c r="C4" s="223"/>
-      <c r="D4" s="223"/>
-      <c r="E4" s="223"/>
-      <c r="F4" s="223"/>
-      <c r="G4" s="223"/>
-      <c r="H4" s="231"/>
+      <c r="B4" s="263"/>
+      <c r="C4" s="263"/>
+      <c r="D4" s="263"/>
+      <c r="E4" s="263"/>
+      <c r="F4" s="263"/>
+      <c r="G4" s="263"/>
+      <c r="H4" s="264"/>
     </row>
     <row r="5" spans="1:8" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="232"/>
+      <c r="A5" s="195"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
       <c r="D5" s="89"/>
       <c r="E5" s="89"/>
       <c r="F5" s="89"/>
       <c r="G5" s="89"/>
-      <c r="H5" s="233" t="s">
+      <c r="H5" s="196" t="s">
         <v>230</v>
       </c>
     </row>
@@ -5462,22 +5426,22 @@
         <f>BS!A6</f>
         <v>Previous Year 2024-25</v>
       </c>
-      <c r="B6" s="182" t="s">
+      <c r="B6" s="265" t="s">
         <v>220</v>
       </c>
-      <c r="C6" s="182"/>
-      <c r="D6" s="254" t="str">
+      <c r="C6" s="265"/>
+      <c r="D6" s="207" t="str">
         <f>BS!D6</f>
         <v>Current Year 2025-26</v>
       </c>
-      <c r="E6" s="252" t="str">
+      <c r="E6" s="205" t="str">
         <f>A6</f>
         <v>Previous Year 2024-25</v>
       </c>
-      <c r="F6" s="182" t="s">
+      <c r="F6" s="265" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="182"/>
+      <c r="G6" s="265"/>
       <c r="H6" s="101" t="str">
         <f>D6</f>
         <v>Current Year 2025-26</v>
@@ -5489,7 +5453,7 @@
         <v>242</v>
       </c>
       <c r="C7" s="97"/>
-      <c r="D7" s="255"/>
+      <c r="D7" s="208"/>
       <c r="E7" s="25"/>
       <c r="F7" s="77" t="s">
         <v>237</v>
@@ -5505,7 +5469,7 @@
         <v>71</v>
       </c>
       <c r="C8" s="31"/>
-      <c r="D8" s="256">
+      <c r="D8" s="209">
         <v>16296</v>
       </c>
       <c r="E8" s="20">
@@ -5523,7 +5487,7 @@
       <c r="A9" s="26"/>
       <c r="B9" s="26"/>
       <c r="C9" s="31"/>
-      <c r="D9" s="257"/>
+      <c r="D9" s="210"/>
       <c r="E9" s="20">
         <v>48000</v>
       </c>
@@ -5545,7 +5509,7 @@
       <c r="C10" s="98">
         <v>179811.41</v>
       </c>
-      <c r="D10" s="257"/>
+      <c r="D10" s="210"/>
       <c r="E10" s="20">
         <v>115200</v>
       </c>
@@ -5568,7 +5532,7 @@
         <f>58680+4000</f>
         <v>62680</v>
       </c>
-      <c r="D11" s="256">
+      <c r="D11" s="209">
         <f>SUM(C10:C11)</f>
         <v>242491.41</v>
       </c>
@@ -5587,7 +5551,7 @@
       <c r="A12" s="26"/>
       <c r="B12" s="26"/>
       <c r="C12" s="31"/>
-      <c r="D12" s="257"/>
+      <c r="D12" s="210"/>
       <c r="E12" s="20">
         <v>18837</v>
       </c>
@@ -5605,7 +5569,7 @@
         <v>243</v>
       </c>
       <c r="C13" s="97"/>
-      <c r="D13" s="255"/>
+      <c r="D13" s="208"/>
       <c r="E13" s="20">
         <v>31550</v>
       </c>
@@ -5628,7 +5592,7 @@
       <c r="C14" s="31">
         <v>41296</v>
       </c>
-      <c r="D14" s="257"/>
+      <c r="D14" s="210"/>
       <c r="E14" s="20">
         <v>2132</v>
       </c>
@@ -5650,7 +5614,7 @@
       <c r="C15" s="32">
         <v>73240</v>
       </c>
-      <c r="D15" s="256">
+      <c r="D15" s="209">
         <f>SUM(C14:C15)</f>
         <v>114536</v>
       </c>
@@ -5669,7 +5633,7 @@
       <c r="A16" s="26"/>
       <c r="B16" s="26"/>
       <c r="C16" s="31"/>
-      <c r="D16" s="258"/>
+      <c r="D16" s="211"/>
       <c r="E16" s="20">
         <v>6000</v>
       </c>
@@ -5687,7 +5651,7 @@
         <v>244</v>
       </c>
       <c r="C17" s="97"/>
-      <c r="D17" s="255"/>
+      <c r="D17" s="208"/>
       <c r="E17" s="20">
         <v>40452</v>
       </c>
@@ -5709,7 +5673,7 @@
       <c r="C18" s="31">
         <v>65400</v>
       </c>
-      <c r="D18" s="257"/>
+      <c r="D18" s="210"/>
       <c r="E18" s="20">
         <v>5000</v>
       </c>
@@ -5734,7 +5698,7 @@
       <c r="C19" s="31">
         <v>158834</v>
       </c>
-      <c r="D19" s="257"/>
+      <c r="D19" s="210"/>
       <c r="E19" s="27"/>
       <c r="F19" s="26"/>
       <c r="G19" s="31"/>
@@ -5750,7 +5714,7 @@
       <c r="C20" s="31">
         <v>-152099</v>
       </c>
-      <c r="D20" s="257"/>
+      <c r="D20" s="210"/>
       <c r="E20" s="27"/>
       <c r="F20" s="26"/>
       <c r="G20" s="31"/>
@@ -5766,7 +5730,7 @@
       <c r="C21" s="31">
         <v>7730</v>
       </c>
-      <c r="D21" s="257"/>
+      <c r="D21" s="210"/>
       <c r="E21" s="30"/>
       <c r="F21" s="77" t="s">
         <v>238</v>
@@ -5784,7 +5748,7 @@
       <c r="C22" s="31">
         <v>1150</v>
       </c>
-      <c r="D22" s="257"/>
+      <c r="D22" s="210"/>
       <c r="E22" s="20">
         <v>9048</v>
       </c>
@@ -5806,7 +5770,7 @@
       <c r="C23" s="31">
         <v>7788</v>
       </c>
-      <c r="D23" s="257"/>
+      <c r="D23" s="210"/>
       <c r="E23" s="27"/>
       <c r="F23" s="26"/>
       <c r="G23" s="31"/>
@@ -5822,7 +5786,7 @@
       <c r="C24" s="32">
         <v>6490</v>
       </c>
-      <c r="D24" s="256">
+      <c r="D24" s="209">
         <f>SUM(C18:C24)</f>
         <v>95293</v>
       </c>
@@ -5838,7 +5802,7 @@
       <c r="A25" s="21"/>
       <c r="B25" s="26"/>
       <c r="C25" s="31"/>
-      <c r="D25" s="257"/>
+      <c r="D25" s="210"/>
       <c r="E25" s="30">
         <v>1402</v>
       </c>
@@ -5856,7 +5820,7 @@
         <v>245</v>
       </c>
       <c r="C26" s="97"/>
-      <c r="D26" s="255"/>
+      <c r="D26" s="208"/>
       <c r="E26" s="20">
         <v>17385</v>
       </c>
@@ -5881,7 +5845,7 @@
       <c r="C27" s="31">
         <v>264000</v>
       </c>
-      <c r="D27" s="257"/>
+      <c r="D27" s="210"/>
       <c r="E27" s="20"/>
       <c r="F27" s="26"/>
       <c r="G27" s="91"/>
@@ -5897,7 +5861,7 @@
       <c r="C28" s="31">
         <v>5216</v>
       </c>
-      <c r="D28" s="257"/>
+      <c r="D28" s="210"/>
       <c r="E28" s="20">
         <v>526740</v>
       </c>
@@ -5920,7 +5884,7 @@
         <f>'Sch II Fixed Asset'!G10</f>
         <v>27751</v>
       </c>
-      <c r="D29" s="257"/>
+      <c r="D29" s="210"/>
       <c r="E29" s="27">
         <v>0</v>
       </c>
@@ -5942,7 +5906,7 @@
       <c r="C30" s="31">
         <v>24180</v>
       </c>
-      <c r="D30" s="257"/>
+      <c r="D30" s="210"/>
       <c r="E30" s="20">
         <v>-91625</v>
       </c>
@@ -5965,7 +5929,7 @@
       <c r="C31" s="31">
         <v>826</v>
       </c>
-      <c r="D31" s="257"/>
+      <c r="D31" s="210"/>
       <c r="E31" s="20">
         <v>-83494</v>
       </c>
@@ -5988,7 +5952,7 @@
       <c r="C32" s="32">
         <v>2800</v>
       </c>
-      <c r="D32" s="256">
+      <c r="D32" s="209">
         <f>SUM(C27:C32)</f>
         <v>324773</v>
       </c>
@@ -6008,7 +5972,7 @@
       <c r="A33" s="26"/>
       <c r="B33" s="26"/>
       <c r="C33" s="31"/>
-      <c r="D33" s="257"/>
+      <c r="D33" s="210"/>
       <c r="E33" s="20">
         <v>-204874</v>
       </c>
@@ -6027,7 +5991,7 @@
         <v>246</v>
       </c>
       <c r="C34" s="97"/>
-      <c r="D34" s="255"/>
+      <c r="D34" s="208"/>
       <c r="E34" s="20">
         <v>-76212</v>
       </c>
@@ -6051,7 +6015,7 @@
         <f>42000+9500</f>
         <v>51500</v>
       </c>
-      <c r="D35" s="257"/>
+      <c r="D35" s="210"/>
       <c r="E35" s="27">
         <v>-11780</v>
       </c>
@@ -6077,7 +6041,7 @@
       <c r="C36" s="31">
         <v>19588</v>
       </c>
-      <c r="D36" s="257"/>
+      <c r="D36" s="210"/>
       <c r="E36" s="27"/>
       <c r="F36" s="26"/>
       <c r="G36" s="31"/>
@@ -6093,7 +6057,7 @@
       <c r="C37" s="31">
         <v>1884</v>
       </c>
-      <c r="D37" s="257"/>
+      <c r="D37" s="210"/>
       <c r="E37" s="27">
         <v>3500</v>
       </c>
@@ -6115,7 +6079,7 @@
       <c r="C38" s="31">
         <v>2570</v>
       </c>
-      <c r="D38" s="257"/>
+      <c r="D38" s="210"/>
       <c r="E38" s="27"/>
       <c r="F38" s="26"/>
       <c r="G38" s="31"/>
@@ -6131,7 +6095,7 @@
       <c r="C39" s="31">
         <v>60</v>
       </c>
-      <c r="D39" s="257"/>
+      <c r="D39" s="210"/>
       <c r="E39" s="27"/>
       <c r="F39" s="26"/>
       <c r="G39" s="31"/>
@@ -6147,7 +6111,7 @@
       <c r="C40" s="31">
         <v>8100</v>
       </c>
-      <c r="D40" s="257"/>
+      <c r="D40" s="210"/>
       <c r="E40" s="27"/>
       <c r="F40" s="26"/>
       <c r="G40" s="31"/>
@@ -6163,7 +6127,7 @@
       <c r="C41" s="31">
         <v>200</v>
       </c>
-      <c r="D41" s="257"/>
+      <c r="D41" s="210"/>
       <c r="E41" s="27"/>
       <c r="F41" s="26"/>
       <c r="G41" s="31"/>
@@ -6179,7 +6143,7 @@
       <c r="C42" s="31">
         <v>25670</v>
       </c>
-      <c r="D42" s="257"/>
+      <c r="D42" s="210"/>
       <c r="E42" s="27"/>
       <c r="F42" s="26"/>
       <c r="G42" s="31"/>
@@ -6195,7 +6159,7 @@
       <c r="C43" s="31">
         <v>250</v>
       </c>
-      <c r="D43" s="257"/>
+      <c r="D43" s="210"/>
       <c r="E43" s="27"/>
       <c r="F43" s="26"/>
       <c r="G43" s="31"/>
@@ -6205,7 +6169,7 @@
       <c r="A44" s="26"/>
       <c r="B44" s="26"/>
       <c r="C44" s="31"/>
-      <c r="D44" s="256">
+      <c r="D44" s="209">
         <f>SUM(C35:C43)</f>
         <v>109822</v>
       </c>
@@ -6220,7 +6184,7 @@
         <v>241</v>
       </c>
       <c r="C45" s="98"/>
-      <c r="D45" s="257"/>
+      <c r="D45" s="210"/>
       <c r="E45" s="27"/>
       <c r="F45" s="26"/>
       <c r="G45" s="31"/>
@@ -6234,7 +6198,7 @@
         <v>170</v>
       </c>
       <c r="C46" s="31"/>
-      <c r="D46" s="259">
+      <c r="D46" s="212">
         <f>ROUND((H48-SUM(D8:D44))*0.25,0)</f>
         <v>10602</v>
       </c>
@@ -6251,7 +6215,7 @@
         <v>143</v>
       </c>
       <c r="C47" s="31"/>
-      <c r="D47" s="260">
+      <c r="D47" s="213">
         <f>H48-SUM(D8:D46)</f>
         <v>31804.589999999967</v>
       </c>
@@ -6265,125 +6229,116 @@
         <f>SUM(A7:A47)</f>
         <v>941527</v>
       </c>
-      <c r="B48" s="183" t="s">
+      <c r="B48" s="268" t="s">
         <v>28</v>
       </c>
-      <c r="C48" s="183"/>
-      <c r="D48" s="261">
+      <c r="C48" s="268"/>
+      <c r="D48" s="214">
         <f>SUM(D7:D47)</f>
         <v>945618</v>
       </c>
-      <c r="E48" s="253">
+      <c r="E48" s="206">
         <f>SUM(E8:E47)</f>
         <v>941527</v>
       </c>
-      <c r="F48" s="183" t="s">
+      <c r="F48" s="268" t="s">
         <v>28</v>
       </c>
-      <c r="G48" s="183"/>
+      <c r="G48" s="268"/>
       <c r="H48" s="75">
         <f>SUM(H8:H47)</f>
         <v>945618</v>
       </c>
     </row>
-    <row r="49" spans="1:10" s="197" customFormat="1" ht="9.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="194"/>
-      <c r="B49" s="234"/>
+    <row r="49" spans="1:10" s="175" customFormat="1" ht="9.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="173"/>
+      <c r="B49" s="152"/>
       <c r="C49" s="19"/>
       <c r="D49" s="70"/>
-      <c r="E49" s="235"/>
-      <c r="F49" s="235"/>
-      <c r="G49" s="235"/>
-      <c r="H49" s="196"/>
-      <c r="J49" s="198"/>
-    </row>
-    <row r="50" spans="1:10" s="197" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="199" t="s">
+      <c r="E49" s="254"/>
+      <c r="F49" s="254"/>
+      <c r="G49" s="254"/>
+      <c r="H49" s="174"/>
+      <c r="J49" s="176"/>
+    </row>
+    <row r="50" spans="1:10" s="175" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="177" t="s">
         <v>84</v>
       </c>
-      <c r="B50" s="236"/>
-      <c r="C50" s="236"/>
-      <c r="D50" s="200"/>
-      <c r="E50" s="201"/>
-      <c r="F50" s="236"/>
-      <c r="G50" s="201"/>
-      <c r="H50" s="202"/>
-      <c r="J50" s="198"/>
-    </row>
-    <row r="51" spans="1:10" s="197" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="203"/>
-      <c r="B51" s="236"/>
-      <c r="C51" s="236"/>
-      <c r="D51" s="204"/>
-      <c r="E51" s="205"/>
-      <c r="F51" s="237" t="s">
+      <c r="D50" s="178"/>
+      <c r="E50" s="179"/>
+      <c r="G50" s="179"/>
+      <c r="H50" s="180"/>
+      <c r="J50" s="176"/>
+    </row>
+    <row r="51" spans="1:10" s="175" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="181"/>
+      <c r="D51" s="182"/>
+      <c r="E51" s="183"/>
+      <c r="F51" s="255" t="s">
         <v>610</v>
       </c>
-      <c r="G51" s="237"/>
-      <c r="H51" s="207"/>
-      <c r="J51" s="198"/>
-    </row>
-    <row r="52" spans="1:10" s="197" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="203"/>
-      <c r="B52" s="236"/>
-      <c r="C52" s="236"/>
-      <c r="D52" s="204"/>
-      <c r="E52" s="205"/>
-      <c r="F52" s="238"/>
-      <c r="G52" s="205"/>
-      <c r="H52" s="209"/>
-      <c r="J52" s="198"/>
-    </row>
-    <row r="53" spans="1:10" s="197" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="203"/>
-      <c r="B53" s="236"/>
-      <c r="C53" s="236"/>
-      <c r="D53" s="204"/>
-      <c r="E53" s="205"/>
-      <c r="F53" s="238"/>
-      <c r="G53" s="205"/>
-      <c r="H53" s="209"/>
-      <c r="I53" s="210"/>
-    </row>
-    <row r="54" spans="1:10" s="197" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="211" t="s">
+      <c r="G51" s="255"/>
+      <c r="H51" s="256"/>
+      <c r="J51" s="176"/>
+    </row>
+    <row r="52" spans="1:10" s="175" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="181"/>
+      <c r="D52" s="182"/>
+      <c r="E52" s="183"/>
+      <c r="F52" s="184"/>
+      <c r="G52" s="183"/>
+      <c r="H52" s="185"/>
+      <c r="J52" s="176"/>
+    </row>
+    <row r="53" spans="1:10" s="175" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="181"/>
+      <c r="D53" s="182"/>
+      <c r="E53" s="183"/>
+      <c r="F53" s="184"/>
+      <c r="G53" s="183"/>
+      <c r="H53" s="185"/>
+      <c r="I53" s="186"/>
+    </row>
+    <row r="54" spans="1:10" s="175" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="187" t="s">
         <v>611</v>
       </c>
-      <c r="B54" s="239"/>
-      <c r="C54" s="240"/>
-      <c r="D54" s="204"/>
-      <c r="E54" s="205"/>
-      <c r="F54" s="238"/>
-      <c r="G54" s="205"/>
-      <c r="H54" s="209"/>
-      <c r="I54" s="210"/>
-    </row>
-    <row r="55" spans="1:10" s="197" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="214" t="s">
+      <c r="B54" s="188"/>
+      <c r="C54" s="189"/>
+      <c r="D54" s="182"/>
+      <c r="E54" s="183"/>
+      <c r="F54" s="184"/>
+      <c r="G54" s="183"/>
+      <c r="H54" s="185"/>
+      <c r="I54" s="186"/>
+    </row>
+    <row r="55" spans="1:10" s="175" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="190" t="s">
         <v>612</v>
       </c>
-      <c r="B55" s="239"/>
-      <c r="C55" s="240"/>
-      <c r="D55" s="204"/>
-      <c r="E55" s="205"/>
-      <c r="F55" s="238"/>
-      <c r="G55" s="205"/>
-      <c r="H55" s="209"/>
-      <c r="I55" s="210"/>
+      <c r="B55" s="188"/>
+      <c r="C55" s="189"/>
+      <c r="D55" s="182"/>
+      <c r="E55" s="183"/>
+      <c r="F55" s="184"/>
+      <c r="G55" s="183"/>
+      <c r="H55" s="185"/>
+      <c r="I55" s="186"/>
     </row>
     <row r="56" spans="1:10" s="95" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="214" t="s">
+      <c r="A56" s="190" t="s">
+        <v>615</v>
+      </c>
+      <c r="B56" s="188"/>
+      <c r="C56" s="189"/>
+      <c r="D56" s="182"/>
+      <c r="E56" s="183"/>
+      <c r="F56" s="257" t="s">
         <v>613</v>
       </c>
-      <c r="B56" s="239"/>
-      <c r="C56" s="240"/>
-      <c r="D56" s="204"/>
-      <c r="E56" s="205"/>
-      <c r="F56" s="241" t="s">
-        <v>614</v>
-      </c>
-      <c r="G56" s="241"/>
-      <c r="H56" s="216"/>
+      <c r="G56" s="257"/>
+      <c r="H56" s="258"/>
       <c r="I56" s="151">
         <f>A48-E48</f>
         <v>0</v>
@@ -6393,17 +6348,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:10" s="197" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="217">
+    <row r="57" spans="1:10" s="175" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="242">
         <v>46235</v>
       </c>
-      <c r="B57" s="218"/>
-      <c r="C57" s="218"/>
-      <c r="D57" s="219"/>
-      <c r="E57" s="220"/>
-      <c r="F57" s="221"/>
-      <c r="G57" s="220"/>
-      <c r="H57" s="222"/>
+      <c r="B57" s="243"/>
+      <c r="C57" s="243"/>
+      <c r="D57" s="191"/>
+      <c r="E57" s="192"/>
+      <c r="F57" s="193"/>
+      <c r="G57" s="192"/>
+      <c r="H57" s="194"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="I58" s="27"/>
@@ -6458,39 +6413,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="271" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="174"/>
-      <c r="C1" s="174"/>
-      <c r="D1" s="174"/>
-      <c r="E1" s="174"/>
-      <c r="F1" s="174"/>
-      <c r="G1" s="174"/>
-      <c r="H1" s="174"/>
-      <c r="I1" s="174"/>
-      <c r="J1" s="174"/>
-      <c r="K1" s="174"/>
-      <c r="L1" s="174"/>
-      <c r="M1" s="174"/>
-      <c r="N1" s="174"/>
+      <c r="B1" s="271"/>
+      <c r="C1" s="271"/>
+      <c r="D1" s="271"/>
+      <c r="E1" s="271"/>
+      <c r="F1" s="271"/>
+      <c r="G1" s="271"/>
+      <c r="H1" s="271"/>
+      <c r="I1" s="271"/>
+      <c r="J1" s="271"/>
+      <c r="K1" s="271"/>
+      <c r="L1" s="271"/>
+      <c r="M1" s="271"/>
+      <c r="N1" s="271"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B2" s="184" t="s">
+      <c r="B2" s="269" t="s">
         <v>365</v>
       </c>
-      <c r="C2" s="184"/>
-      <c r="D2" s="184"/>
-      <c r="E2" s="184"/>
-      <c r="F2" s="184"/>
-      <c r="G2" s="184"/>
-      <c r="H2" s="184"/>
-      <c r="I2" s="184"/>
-      <c r="J2" s="184"/>
-      <c r="K2" s="184"/>
-      <c r="L2" s="184"/>
-      <c r="M2" s="184"/>
-      <c r="N2" s="184"/>
+      <c r="C2" s="269"/>
+      <c r="D2" s="269"/>
+      <c r="E2" s="269"/>
+      <c r="F2" s="269"/>
+      <c r="G2" s="269"/>
+      <c r="H2" s="269"/>
+      <c r="I2" s="269"/>
+      <c r="J2" s="269"/>
+      <c r="K2" s="269"/>
+      <c r="L2" s="269"/>
+      <c r="M2" s="269"/>
+      <c r="N2" s="269"/>
     </row>
     <row r="3" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="45" t="s">
@@ -7297,7 +7252,7 @@
       <c r="B21" s="155">
         <v>6605400016067</v>
       </c>
-      <c r="C21" s="262" t="s">
+      <c r="C21" s="215" t="s">
         <v>349</v>
       </c>
       <c r="D21" s="104">
@@ -7699,7 +7654,7 @@
       <c r="B31" s="118" t="s">
         <v>255</v>
       </c>
-      <c r="C31" s="263" t="s">
+      <c r="C31" s="216" t="s">
         <v>142</v>
       </c>
       <c r="D31" s="159">
@@ -7933,7 +7888,7 @@
       <c r="B36" s="122" t="s">
         <v>354</v>
       </c>
-      <c r="C36" s="262" t="s">
+      <c r="C36" s="215" t="s">
         <v>334</v>
       </c>
       <c r="D36" s="160">
@@ -8317,7 +8272,7 @@
       <c r="B46" s="161" t="s">
         <v>256</v>
       </c>
-      <c r="C46" s="264" t="s">
+      <c r="C46" s="217" t="s">
         <v>142</v>
       </c>
       <c r="D46" s="109">
@@ -8364,7 +8319,7 @@
       <c r="B47" s="121">
         <v>220738</v>
       </c>
-      <c r="C47" s="263" t="s">
+      <c r="C47" s="216" t="s">
         <v>281</v>
       </c>
       <c r="D47" s="18">
@@ -8411,7 +8366,7 @@
       <c r="B48" s="121">
         <v>116861</v>
       </c>
-      <c r="C48" s="263" t="s">
+      <c r="C48" s="216" t="s">
         <v>289</v>
       </c>
       <c r="D48" s="18">
@@ -8458,7 +8413,7 @@
       <c r="B49" s="121">
         <v>116845</v>
       </c>
-      <c r="C49" s="263" t="s">
+      <c r="C49" s="216" t="s">
         <v>289</v>
       </c>
       <c r="D49" s="18">
@@ -8500,7 +8455,7 @@
       <c r="B50" s="155">
         <v>6605500001645</v>
       </c>
-      <c r="C50" s="265" t="s">
+      <c r="C50" s="218" t="s">
         <v>334</v>
       </c>
       <c r="D50" s="109">
@@ -8662,7 +8617,7 @@
       <c r="B55" s="162" t="s">
         <v>253</v>
       </c>
-      <c r="C55" s="263" t="s">
+      <c r="C55" s="216" t="s">
         <v>142</v>
       </c>
       <c r="D55" s="18">
@@ -9231,7 +9186,7 @@
       <c r="B67" s="122">
         <v>281681</v>
       </c>
-      <c r="C67" s="262" t="s">
+      <c r="C67" s="215" t="s">
         <v>279</v>
       </c>
       <c r="D67" s="104">
@@ -9278,7 +9233,7 @@
       <c r="B68" s="122" t="s">
         <v>356</v>
       </c>
-      <c r="C68" s="262" t="s">
+      <c r="C68" s="215" t="s">
         <v>357</v>
       </c>
       <c r="D68" s="104">
@@ -9320,31 +9275,31 @@
       <c r="B69" s="156"/>
       <c r="C69" s="80"/>
       <c r="D69" s="82">
-        <f>SUM(D54:D68)</f>
+        <f t="shared" ref="D69:J69" si="7">SUM(D54:D68)</f>
         <v>1565264</v>
       </c>
       <c r="E69" s="82">
-        <f>SUM(E54:E68)</f>
+        <f t="shared" si="7"/>
         <v>7525</v>
       </c>
       <c r="F69" s="82">
-        <f>SUM(F54:F68)</f>
+        <f t="shared" si="7"/>
         <v>15362</v>
       </c>
       <c r="G69" s="82">
-        <f>SUM(G54:G68)</f>
+        <f t="shared" si="7"/>
         <v>24881</v>
       </c>
       <c r="H69" s="82">
-        <f>SUM(H54:H68)</f>
+        <f t="shared" si="7"/>
         <v>45202</v>
       </c>
       <c r="I69" s="82">
-        <f>SUM(I54:I68)</f>
+        <f t="shared" si="7"/>
         <v>80517</v>
       </c>
       <c r="J69" s="82">
-        <f>SUM(J54:J68)</f>
+        <f t="shared" si="7"/>
         <v>1738751</v>
       </c>
       <c r="K69" s="83"/>
@@ -9449,7 +9404,7 @@
         <v>1328</v>
       </c>
       <c r="J73" s="5">
-        <f t="shared" ref="J73:J78" si="7">SUM(D73:I73)</f>
+        <f t="shared" ref="J73:J78" si="8">SUM(D73:I73)</f>
         <v>21921</v>
       </c>
       <c r="K73" s="5" t="s">
@@ -9499,7 +9454,7 @@
         <v>811</v>
       </c>
       <c r="J74" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>16608</v>
       </c>
       <c r="K74" s="5" t="s">
@@ -9546,7 +9501,7 @@
         <v>1292</v>
       </c>
       <c r="J75" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>21310</v>
       </c>
       <c r="K75" s="5" t="s">
@@ -9641,7 +9596,7 @@
         <v>709</v>
       </c>
       <c r="J77" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>11679</v>
       </c>
       <c r="K77" s="5" t="s">
@@ -9664,7 +9619,7 @@
       <c r="B78" s="155">
         <v>220754</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="215" t="s">
         <v>281</v>
       </c>
       <c r="D78" s="104">
@@ -9688,7 +9643,7 @@
         <v>659</v>
       </c>
       <c r="J78" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>10873</v>
       </c>
       <c r="K78" s="105" t="s">
@@ -9713,19 +9668,19 @@
         <v>107477</v>
       </c>
       <c r="E79" s="82">
-        <f t="shared" ref="E79:H79" si="8">SUM(E72:E78)</f>
+        <f t="shared" ref="E79:H79" si="9">SUM(E72:E78)</f>
         <v>459</v>
       </c>
       <c r="F79" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1226</v>
       </c>
       <c r="G79" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2628</v>
       </c>
       <c r="H79" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3863</v>
       </c>
       <c r="I79" s="82">
@@ -9836,7 +9791,7 @@
         <v>3875</v>
       </c>
       <c r="J83" s="5">
-        <f t="shared" ref="J83:J86" si="9">SUM(D83:I83)</f>
+        <f t="shared" ref="J83:J86" si="10">SUM(D83:I83)</f>
         <v>63937</v>
       </c>
       <c r="K83" s="13" t="s">
@@ -9884,7 +9839,7 @@
         <v>840</v>
       </c>
       <c r="J84" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>13402</v>
       </c>
       <c r="K84" s="13" t="s">
@@ -9930,7 +9885,7 @@
         <v>1641</v>
       </c>
       <c r="J85" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>35483</v>
       </c>
       <c r="K85" s="13" t="s">
@@ -9977,7 +9932,7 @@
         <v>658</v>
       </c>
       <c r="J86" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10872</v>
       </c>
       <c r="K86" s="13" t="s">
@@ -10002,27 +9957,27 @@
         <v>129252</v>
       </c>
       <c r="E87" s="82">
-        <f t="shared" ref="E87:J87" si="10">SUM(E82:E86)</f>
+        <f t="shared" ref="E87:J87" si="11">SUM(E82:E86)</f>
         <v>0</v>
       </c>
       <c r="F87" s="82">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="G87" s="82">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>109</v>
       </c>
       <c r="H87" s="82">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2264</v>
       </c>
       <c r="I87" s="82">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>7977</v>
       </c>
       <c r="J87" s="82">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>139602</v>
       </c>
       <c r="K87" s="85"/>
@@ -10137,7 +10092,7 @@
         <v>13805</v>
       </c>
       <c r="J91" s="5">
-        <f t="shared" ref="J91:J92" si="11">SUM(D91:I91)</f>
+        <f t="shared" ref="J91:J92" si="12">SUM(D91:I91)</f>
         <v>225838</v>
       </c>
       <c r="K91" s="5" t="s">
@@ -10184,7 +10139,7 @@
         <v>19287</v>
       </c>
       <c r="J92" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>318284</v>
       </c>
       <c r="K92" s="5" t="s">
@@ -10209,32 +10164,32 @@
         <v>722007</v>
       </c>
       <c r="E93" s="82">
-        <f t="shared" ref="E93:L93" si="12">SUM(E90:E92)</f>
+        <f t="shared" ref="E93:L93" si="13">SUM(E90:E92)</f>
         <v>0</v>
       </c>
       <c r="F93" s="82">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G93" s="82">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>11176</v>
       </c>
       <c r="H93" s="82">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>26385</v>
       </c>
       <c r="I93" s="82">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>38348</v>
       </c>
       <c r="J93" s="82">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>797916</v>
       </c>
       <c r="K93" s="85"/>
       <c r="L93" s="82">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>866699</v>
       </c>
       <c r="M93" s="80"/>
@@ -10306,15 +10261,15 @@
         <v>14000</v>
       </c>
       <c r="E97" s="82">
-        <f t="shared" ref="E97:G97" si="13">SUM(E96:E96)</f>
+        <f t="shared" ref="E97:G97" si="14">SUM(E96:E96)</f>
         <v>0</v>
       </c>
       <c r="F97" s="82">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="G97" s="82">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H97" s="111">
@@ -10324,7 +10279,7 @@
         <v>0</v>
       </c>
       <c r="J97" s="82">
-        <f t="shared" ref="J97" si="14">SUM(J96:J96)</f>
+        <f t="shared" ref="J97" si="15">SUM(J96:J96)</f>
         <v>14000</v>
       </c>
       <c r="K97" s="85"/>
@@ -10343,10 +10298,10 @@
     </row>
     <row r="99" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="80"/>
-      <c r="B99" s="185" t="s">
+      <c r="B99" s="270" t="s">
         <v>57</v>
       </c>
-      <c r="C99" s="185"/>
+      <c r="C99" s="270"/>
       <c r="D99" s="48">
         <f>D22+D37+D51+D69+D79+D87+D93+D97</f>
         <v>8627401</v>
@@ -10356,19 +10311,19 @@
         <v>9050</v>
       </c>
       <c r="F99" s="48">
-        <f t="shared" ref="F99:I99" si="15">F22+F37+F51+F69+F79+F87+F93+F97</f>
+        <f t="shared" ref="F99:I99" si="16">F22+F37+F51+F69+F79+F87+F93+F97</f>
         <v>30323</v>
       </c>
       <c r="G99" s="48">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>92231</v>
       </c>
       <c r="H99" s="48">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>256109</v>
       </c>
       <c r="I99" s="48">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>457973</v>
       </c>
       <c r="J99" s="48">
@@ -10427,41 +10382,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="193" t="s">
+      <c r="A1" s="245" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="193"/>
-      <c r="G1" s="193"/>
-      <c r="H1" s="193"/>
+      <c r="B1" s="245"/>
+      <c r="C1" s="245"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="245"/>
+      <c r="F1" s="245"/>
+      <c r="G1" s="245"/>
+      <c r="H1" s="245"/>
     </row>
     <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A2" s="266" t="s">
+      <c r="A2" s="272" t="s">
         <v>582</v>
       </c>
-      <c r="B2" s="266"/>
-      <c r="C2" s="266"/>
-      <c r="D2" s="266"/>
-      <c r="E2" s="266"/>
-      <c r="F2" s="266"/>
-      <c r="G2" s="266"/>
-      <c r="H2" s="266"/>
+      <c r="B2" s="272"/>
+      <c r="C2" s="272"/>
+      <c r="D2" s="272"/>
+      <c r="E2" s="272"/>
+      <c r="F2" s="272"/>
+      <c r="G2" s="272"/>
+      <c r="H2" s="272"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="37"/>
-      <c r="B3" s="186" t="s">
+      <c r="B3" s="273" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="187"/>
-      <c r="D3" s="187"/>
-      <c r="E3" s="187"/>
-      <c r="F3" s="186" t="s">
+      <c r="C3" s="274"/>
+      <c r="D3" s="274"/>
+      <c r="E3" s="274"/>
+      <c r="F3" s="273" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="186"/>
+      <c r="G3" s="273"/>
       <c r="H3" s="42" t="s">
         <v>59</v>
       </c>
@@ -10688,353 +10643,353 @@
   <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" style="197" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" style="197" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.33203125" style="197" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" style="210" customWidth="1"/>
-    <col min="5" max="6" width="9.109375" style="197"/>
-    <col min="7" max="7" width="9.5546875" style="197" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="197"/>
+    <col min="1" max="1" width="6.88671875" style="175" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" style="175" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.33203125" style="175" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" style="186" customWidth="1"/>
+    <col min="5" max="6" width="9.109375" style="175"/>
+    <col min="7" max="7" width="9.5546875" style="175" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="175"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="275" t="s">
+      <c r="A1" s="277" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="275"/>
-      <c r="C1" s="275"/>
-      <c r="D1" s="275"/>
+      <c r="B1" s="277"/>
+      <c r="C1" s="277"/>
+      <c r="D1" s="277"/>
       <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="189" t="s">
+      <c r="A2" s="276" t="s">
         <v>583</v>
       </c>
-      <c r="B2" s="189"/>
-      <c r="C2" s="189"/>
-      <c r="D2" s="189"/>
+      <c r="B2" s="276"/>
+      <c r="C2" s="276"/>
+      <c r="D2" s="276"/>
     </row>
     <row r="3" spans="1:5" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="287" t="s">
+      <c r="A3" s="238" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="287" t="s">
+      <c r="B3" s="238" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="287" t="s">
+      <c r="C3" s="238" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="288" t="s">
+      <c r="D3" s="239" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="270">
+      <c r="A4" s="222">
         <v>1</v>
       </c>
-      <c r="B4" s="270">
+      <c r="B4" s="222">
         <v>302</v>
       </c>
       <c r="C4" s="165" t="s">
         <v>173</v>
       </c>
-      <c r="D4" s="277">
+      <c r="D4" s="228">
         <v>8815</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="267">
+      <c r="A5" s="219">
         <v>2</v>
       </c>
-      <c r="B5" s="269">
+      <c r="B5" s="221">
         <v>104</v>
       </c>
       <c r="C5" s="166" t="s">
         <v>587</v>
       </c>
-      <c r="D5" s="268">
+      <c r="D5" s="220">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="267">
+      <c r="A6" s="219">
         <v>3</v>
       </c>
-      <c r="B6" s="269">
+      <c r="B6" s="221">
         <v>201</v>
       </c>
       <c r="C6" s="166" t="s">
         <v>588</v>
       </c>
-      <c r="D6" s="268">
+      <c r="D6" s="220">
         <v>2794</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="267">
+      <c r="A7" s="219">
         <v>4</v>
       </c>
-      <c r="B7" s="269">
+      <c r="B7" s="221">
         <v>202</v>
       </c>
       <c r="C7" s="166" t="s">
         <v>589</v>
       </c>
-      <c r="D7" s="268">
+      <c r="D7" s="220">
         <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="267">
+      <c r="A8" s="219">
         <v>5</v>
       </c>
-      <c r="B8" s="269">
+      <c r="B8" s="221">
         <v>204</v>
       </c>
       <c r="C8" s="166" t="s">
         <v>590</v>
       </c>
-      <c r="D8" s="268">
+      <c r="D8" s="220">
         <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="274"/>
-      <c r="B9" s="285"/>
+      <c r="A9" s="226"/>
+      <c r="B9" s="236"/>
       <c r="C9" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="286">
+      <c r="D9" s="237">
         <f>SUM(D4:D8)</f>
         <v>11805</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="19.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="189" t="s">
+      <c r="A11" s="276" t="s">
         <v>584</v>
       </c>
-      <c r="B11" s="189"/>
-      <c r="C11" s="189"/>
-      <c r="D11" s="189"/>
+      <c r="B11" s="276"/>
+      <c r="C11" s="276"/>
+      <c r="D11" s="276"/>
     </row>
     <row r="12" spans="1:5" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="287" t="s">
+      <c r="A12" s="238" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="287" t="s">
+      <c r="B12" s="238" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="287" t="s">
+      <c r="C12" s="238" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="288" t="s">
+      <c r="D12" s="239" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="270">
+      <c r="A13" s="222">
         <v>1</v>
       </c>
-      <c r="B13" s="270">
+      <c r="B13" s="222">
         <v>101</v>
       </c>
-      <c r="C13" s="271" t="s">
+      <c r="C13" s="223" t="s">
         <v>137</v>
       </c>
-      <c r="D13" s="276">
+      <c r="D13" s="227">
         <v>10000</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="267">
+      <c r="A14" s="219">
         <v>2</v>
       </c>
-      <c r="B14" s="270">
+      <c r="B14" s="222">
         <v>203</v>
       </c>
       <c r="C14" s="165" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="277">
+      <c r="D14" s="228">
         <v>10000</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="267">
+      <c r="A15" s="219">
         <v>3</v>
       </c>
-      <c r="B15" s="267">
+      <c r="B15" s="219">
         <v>502</v>
       </c>
       <c r="C15" s="166" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="268">
+      <c r="D15" s="220">
         <v>10000</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="267">
+      <c r="A16" s="219">
         <v>4</v>
       </c>
-      <c r="B16" s="267">
+      <c r="B16" s="219">
         <v>503</v>
       </c>
       <c r="C16" s="166" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="268">
+      <c r="D16" s="220">
         <v>10000</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="267">
+      <c r="A17" s="219">
         <v>5</v>
       </c>
-      <c r="B17" s="267">
+      <c r="B17" s="219">
         <v>504</v>
       </c>
       <c r="C17" s="166" t="s">
         <v>174</v>
       </c>
-      <c r="D17" s="268">
+      <c r="D17" s="220">
         <v>10000</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="267">
+      <c r="A18" s="219">
         <v>6</v>
       </c>
-      <c r="B18" s="267">
+      <c r="B18" s="219">
         <v>602</v>
       </c>
       <c r="C18" s="166" t="s">
         <v>275</v>
       </c>
-      <c r="D18" s="268">
+      <c r="D18" s="220">
         <v>10000</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="272">
+      <c r="A19" s="224">
         <v>7</v>
       </c>
-      <c r="B19" s="272" t="s">
+      <c r="B19" s="224" t="s">
         <v>82</v>
       </c>
       <c r="C19" s="167" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="278">
+      <c r="D19" s="229">
         <v>20000</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="274"/>
-      <c r="B20" s="285"/>
+      <c r="A20" s="226"/>
+      <c r="B20" s="236"/>
       <c r="C20" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="286">
+      <c r="D20" s="237">
         <f>SUM(D13:D19)</f>
         <v>80000</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="19.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="189" t="s">
+      <c r="A22" s="276" t="s">
         <v>62</v>
       </c>
-      <c r="B22" s="189"/>
-      <c r="C22" s="189"/>
-      <c r="D22" s="189"/>
+      <c r="B22" s="276"/>
+      <c r="C22" s="276"/>
+      <c r="D22" s="276"/>
     </row>
     <row r="23" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="189" t="s">
+      <c r="A23" s="276" t="s">
         <v>585</v>
       </c>
-      <c r="B23" s="189"/>
-      <c r="C23" s="189"/>
-      <c r="D23" s="189"/>
+      <c r="B23" s="276"/>
+      <c r="C23" s="276"/>
+      <c r="D23" s="276"/>
     </row>
     <row r="24" spans="1:4" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="287" t="s">
+      <c r="A24" s="238" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="287" t="s">
+      <c r="B24" s="238" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="287" t="s">
+      <c r="C24" s="238" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="288" t="s">
+      <c r="D24" s="239" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="270">
+      <c r="A25" s="222">
         <v>1</v>
       </c>
-      <c r="B25" s="273">
+      <c r="B25" s="225">
         <v>203</v>
       </c>
       <c r="C25" s="165" t="s">
         <v>66</v>
       </c>
-      <c r="D25" s="277">
+      <c r="D25" s="228">
         <v>4174</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="270">
+      <c r="A26" s="222">
         <v>2</v>
       </c>
-      <c r="B26" s="273">
+      <c r="B26" s="225">
         <v>102</v>
       </c>
       <c r="C26" s="165" t="s">
         <v>591</v>
       </c>
-      <c r="D26" s="277">
+      <c r="D26" s="228">
         <v>2765</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="270">
+      <c r="A27" s="222">
         <v>3</v>
       </c>
-      <c r="B27" s="273">
+      <c r="B27" s="225">
         <v>403</v>
       </c>
       <c r="C27" s="165" t="s">
         <v>592</v>
       </c>
-      <c r="D27" s="277">
+      <c r="D27" s="228">
         <v>2765</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="270">
+      <c r="A28" s="222">
         <v>4</v>
       </c>
-      <c r="B28" s="273">
+      <c r="B28" s="225">
         <v>404</v>
       </c>
       <c r="C28" s="165" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="277">
+      <c r="D28" s="228">
         <v>22273</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="274"/>
-      <c r="B29" s="285"/>
+      <c r="A29" s="226"/>
+      <c r="B29" s="236"/>
       <c r="C29" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="286">
+      <c r="D29" s="237">
         <f>SUM(D25:D28)</f>
         <v>31977</v>
       </c>
@@ -11042,217 +10997,217 @@
     <row r="30" spans="1:4" ht="19.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="31" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="188" t="s">
+      <c r="A32" s="275" t="s">
         <v>586</v>
       </c>
-      <c r="B32" s="188"/>
-      <c r="C32" s="188"/>
-      <c r="D32" s="188"/>
+      <c r="B32" s="275"/>
+      <c r="C32" s="275"/>
+      <c r="D32" s="275"/>
     </row>
     <row r="33" spans="1:7" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="287" t="s">
+      <c r="A33" s="238" t="s">
         <v>50</v>
       </c>
-      <c r="B33" s="289" t="s">
+      <c r="B33" s="240" t="s">
         <v>180</v>
       </c>
-      <c r="C33" s="290" t="s">
+      <c r="C33" s="241" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="290" t="s">
-        <v>615</v>
+      <c r="D33" s="241" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="279">
+      <c r="A34" s="230">
         <v>1</v>
       </c>
-      <c r="B34" s="282">
+      <c r="B34" s="233">
         <v>381</v>
       </c>
       <c r="C34" s="165" t="s">
         <v>105</v>
       </c>
-      <c r="D34" s="277">
+      <c r="D34" s="228">
         <f>742-126</f>
         <v>616</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="280">
+      <c r="A35" s="231">
         <v>2</v>
       </c>
-      <c r="B35" s="283">
+      <c r="B35" s="234">
         <v>2800</v>
       </c>
       <c r="C35" s="166" t="s">
         <v>16</v>
       </c>
-      <c r="D35" s="268">
+      <c r="D35" s="220">
         <v>2800</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="279">
+      <c r="A36" s="230">
         <v>3</v>
       </c>
-      <c r="B36" s="283">
+      <c r="B36" s="234">
         <v>12690</v>
       </c>
       <c r="C36" s="166" t="s">
         <v>171</v>
       </c>
-      <c r="D36" s="268">
+      <c r="D36" s="220">
         <v>10236</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="280">
+      <c r="A37" s="231">
         <v>4</v>
       </c>
-      <c r="B37" s="283">
+      <c r="B37" s="234">
         <v>14590</v>
       </c>
       <c r="C37" s="166" t="s">
         <v>136</v>
       </c>
-      <c r="D37" s="268">
+      <c r="D37" s="220">
         <v>14149.52</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="279">
+      <c r="A38" s="230">
         <v>5</v>
       </c>
-      <c r="B38" s="283">
+      <c r="B38" s="234">
         <v>18953</v>
       </c>
       <c r="C38" s="166" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="268">
+      <c r="D38" s="220">
         <v>4195</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="280">
+      <c r="A39" s="231">
         <v>6</v>
       </c>
-      <c r="B39" s="284">
+      <c r="B39" s="235">
         <v>6270</v>
       </c>
       <c r="C39" s="167" t="s">
         <v>147</v>
       </c>
-      <c r="D39" s="278">
+      <c r="D39" s="229">
         <v>6270</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="279">
+      <c r="A40" s="230">
         <v>7</v>
       </c>
-      <c r="B40" s="284">
+      <c r="B40" s="235">
         <v>0</v>
       </c>
       <c r="C40" s="167" t="s">
         <v>204</v>
       </c>
-      <c r="D40" s="278">
+      <c r="D40" s="229">
         <v>199</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="280">
+      <c r="A41" s="231">
         <v>8</v>
       </c>
-      <c r="B41" s="284">
+      <c r="B41" s="235">
         <v>147</v>
       </c>
       <c r="C41" s="167" t="s">
         <v>300</v>
       </c>
-      <c r="D41" s="278">
+      <c r="D41" s="229">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="279">
+      <c r="A42" s="230">
         <v>9</v>
       </c>
-      <c r="B42" s="284">
+      <c r="B42" s="235">
         <v>1000</v>
       </c>
       <c r="C42" s="167" t="s">
         <v>117</v>
       </c>
-      <c r="D42" s="278">
+      <c r="D42" s="229">
         <v>1000</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="280">
+      <c r="A43" s="231">
         <v>10</v>
       </c>
-      <c r="B43" s="284">
+      <c r="B43" s="235">
         <v>3500</v>
       </c>
       <c r="C43" s="167" t="s">
         <v>172</v>
       </c>
-      <c r="D43" s="278">
+      <c r="D43" s="229">
         <v>3800</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="279">
+      <c r="A44" s="230">
         <v>11</v>
       </c>
-      <c r="B44" s="284">
+      <c r="B44" s="235">
         <v>1500</v>
       </c>
       <c r="C44" s="167" t="s">
         <v>201</v>
       </c>
-      <c r="D44" s="278">
+      <c r="D44" s="229">
         <v>1500</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="281">
+      <c r="A45" s="232">
         <v>12</v>
       </c>
-      <c r="B45" s="284">
+      <c r="B45" s="235">
         <v>0</v>
       </c>
       <c r="C45" s="167" t="s">
         <v>598</v>
       </c>
-      <c r="D45" s="278">
+      <c r="D45" s="229">
         <v>826</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="274"/>
-      <c r="B46" s="285">
+      <c r="A46" s="226"/>
+      <c r="B46" s="236">
         <v>61831</v>
       </c>
       <c r="C46" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="D46" s="286">
+      <c r="D46" s="237">
         <f>SUM(D34:D45)</f>
         <v>45591.520000000004</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="19.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B47" s="70"/>
-      <c r="C47" s="198"/>
-      <c r="G47" s="198"/>
+      <c r="C47" s="176"/>
+      <c r="G47" s="176"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B48" s="70"/>
-      <c r="C48" s="198"/>
+      <c r="C48" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -11286,18 +11241,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="190" t="s">
+      <c r="A1" s="278" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="190"/>
-      <c r="C1" s="190"/>
+      <c r="B1" s="278"/>
+      <c r="C1" s="278"/>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="184" t="s">
+      <c r="A2" s="269" t="s">
         <v>605</v>
       </c>
-      <c r="B2" s="184"/>
-      <c r="C2" s="184"/>
+      <c r="B2" s="269"/>
+      <c r="C2" s="269"/>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3"/>
@@ -11463,18 +11418,18 @@
       <c r="E12" s="47"/>
     </row>
     <row r="14" spans="1:9" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="190" t="s">
+      <c r="A14" s="278" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="190"/>
-      <c r="C14" s="190"/>
+      <c r="B14" s="278"/>
+      <c r="C14" s="278"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="184" t="s">
+      <c r="A15" s="269" t="s">
         <v>606</v>
       </c>
-      <c r="B15" s="184"/>
-      <c r="C15" s="184"/>
+      <c r="B15" s="269"/>
+      <c r="C15" s="269"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C16" s="1" t="s">
@@ -11506,18 +11461,18 @@
       <c r="C20" s="170"/>
     </row>
     <row r="22" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="190" t="s">
+      <c r="A22" s="278" t="s">
         <v>93</v>
       </c>
-      <c r="B22" s="190"/>
-      <c r="C22" s="190"/>
+      <c r="B22" s="278"/>
+      <c r="C22" s="278"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="184" t="s">
+      <c r="A23" s="269" t="s">
         <v>607</v>
       </c>
-      <c r="B23" s="184"/>
-      <c r="C23" s="184"/>
+      <c r="B23" s="269"/>
+      <c r="C23" s="269"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C24" s="1" t="s">
@@ -11549,18 +11504,18 @@
       <c r="C28" s="170"/>
     </row>
     <row r="30" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="190" t="s">
+      <c r="A30" s="278" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="190"/>
-      <c r="C30" s="190"/>
+      <c r="B30" s="278"/>
+      <c r="C30" s="278"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="184" t="s">
+      <c r="A31" s="269" t="s">
         <v>608</v>
       </c>
-      <c r="B31" s="184"/>
-      <c r="C31" s="184"/>
+      <c r="B31" s="269"/>
+      <c r="C31" s="269"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C32" s="1" t="s">
@@ -11624,12 +11579,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="191" t="s">
+      <c r="A1" s="279" t="s">
         <v>593</v>
       </c>
-      <c r="B1" s="191"/>
-      <c r="C1" s="191"/>
-      <c r="D1" s="191"/>
+      <c r="B1" s="279"/>
+      <c r="C1" s="279"/>
+      <c r="D1" s="279"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
@@ -11649,10 +11604,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="62"/>
-      <c r="B4" s="192" t="s">
+      <c r="B4" s="280" t="s">
         <v>148</v>
       </c>
-      <c r="C4" s="192"/>
+      <c r="C4" s="280"/>
       <c r="D4" s="61" t="s">
         <v>114</v>
       </c>
@@ -11831,13 +11786,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="175" t="s">
+      <c r="A1" s="246" t="s">
         <v>295</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="114" t="s">
